--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -87,7 +87,7 @@
     <t>logF_BusinessProcessName</t>
   </si>
   <si>
-    <t>Framework</t>
+    <t>ACME_CredentialAssetName</t>
   </si>
   <si>
     <t>Orchestrator queue Name. The value must match with the queue name defined on Orchestrator.</t>
@@ -102,7 +102,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
+    <t>Retries handled by Orchestrator queue auto-retry</t>
   </si>
   <si>
     <t>Static part of logging message. Processed Transaction succesful.</t>
@@ -159,7 +159,19 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>ProcessABCQueue</t>
+    <t>ACME_ClientSecurityHash</t>
+  </si>
+  <si>
+    <t>ACME_Credential</t>
+  </si>
+  <si>
+    <t>Name of the Orchestrator credential asset for ACME login</t>
+  </si>
+  <si>
+    <t>ACME_URL</t>
+  </si>
+  <si>
+    <t>ACME System 1 URL from Orchestrator text asset</t>
   </si>
 </sst>
 </file>
@@ -604,13 +616,23 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2815,7 +2837,17 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>Name</t>
   </si>
@@ -172,6 +172,60 @@
   </si>
   <si>
     <t>ACME System 1 URL from Orchestrator text asset</t>
+  </si>
+  <si>
+    <t>SHA1_URL</t>
+  </si>
+  <si>
+    <t>http://www.sha1-online.com/</t>
+  </si>
+  <si>
+    <t>Address of the SHA1 Online hash generator</t>
+  </si>
+  <si>
+    <t>SHA1_Algorithm</t>
+  </si>
+  <si>
+    <t>sha-1</t>
+  </si>
+  <si>
+    <t>Item to select in the hash algorithm dropdown of SHA1 Online</t>
+  </si>
+  <si>
+    <t>ACME_WorkItemType</t>
+  </si>
+  <si>
+    <t>WI5</t>
+  </si>
+  <si>
+    <t>Work item type this process handles; queue items of any other type are rejected as business exceptions</t>
+  </si>
+  <si>
+    <t>ACME_CompletedStatus</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Status set on a work item once its hash comment is added</t>
+  </si>
+  <si>
+    <t>ACME_UpdateSuccessText</t>
+  </si>
+  <si>
+    <t>Work Item was updated accordingly</t>
+  </si>
+  <si>
+    <t>Text of the browser alert ACME shows after a successful work item update</t>
+  </si>
+  <si>
+    <t>KillChromeOnRecovery</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>TRUE to force-kill chrome.exe when applications cannot be closed. Keep FALSE on a machine where a person also uses Chrome</t>
   </si>
 </sst>
 </file>
@@ -633,12 +687,72 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
   <si>
     <t>Name</t>
   </si>
@@ -226,6 +226,45 @@
   </si>
   <si>
     <t>TRUE to force-kill chrome.exe when applications cannot be closed. Keep FALSE on a machine where a person also uses Chrome</t>
+  </si>
+  <si>
+    <t>ExceptionEmail_To</t>
+  </si>
+  <si>
+    <t>Recipient of exception emails (several addresses separated by semicolons). Leave empty to log the message instead of sending it</t>
+  </si>
+  <si>
+    <t>ExceptionEmail_LoginFailedBody</t>
+  </si>
+  <si>
+    <t>Hello, The username or the email is incorrect. Please check and restart Thank you</t>
+  </si>
+  <si>
+    <t>Body of the email sent when ACME rejects the login (text from the PDD)</t>
+  </si>
+  <si>
+    <t>SMTP_Server</t>
+  </si>
+  <si>
+    <t>SMTP server used to send exception emails, for example smtp.gmail.com. Leave empty to log the message instead of sending it</t>
+  </si>
+  <si>
+    <t>SMTP_Port</t>
+  </si>
+  <si>
+    <t>587</t>
+  </si>
+  <si>
+    <t>SMTP port (587 for STARTTLS, 465 for SSL)</t>
+  </si>
+  <si>
+    <t>SMTP_CredentialAssetName</t>
+  </si>
+  <si>
+    <t>SMTP_Credential</t>
+  </si>
+  <si>
+    <t>Name of the Orchestrator credential asset holding the sending mailbox address and its password</t>
   </si>
 </sst>
 </file>
@@ -753,11 +792,55 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/alexandra_veizu_uipath_com/Documents/Documents/Projects/REFrameworkNET5/StudioTemplates/REFramework/contentFiles/any/any/pt2/VisualBasic/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UiPath\ACME_Performer\ACME_ClientHash_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C54E24-BA5C-4BF9-8DAB-2778512EC11B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADB8CDB-FC6F-41FC-A966-B556B226A34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11784" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
   <si>
     <t>Name</t>
   </si>
@@ -162,116 +162,125 @@
     <t>ACME_ClientSecurityHash</t>
   </si>
   <si>
+    <t>Name of the Orchestrator credential asset for ACME login</t>
+  </si>
+  <si>
+    <t>ACME_URL</t>
+  </si>
+  <si>
+    <t>ACME System 1 URL from Orchestrator text asset</t>
+  </si>
+  <si>
+    <t>SHA1_URL</t>
+  </si>
+  <si>
+    <t>http://www.sha1-online.com/</t>
+  </si>
+  <si>
+    <t>Address of the SHA1 Online hash generator</t>
+  </si>
+  <si>
+    <t>SHA1_Algorithm</t>
+  </si>
+  <si>
+    <t>sha-1</t>
+  </si>
+  <si>
+    <t>Item to select in the hash algorithm dropdown of SHA1 Online</t>
+  </si>
+  <si>
+    <t>ACME_WorkItemType</t>
+  </si>
+  <si>
+    <t>WI5</t>
+  </si>
+  <si>
+    <t>Work item type this process handles; queue items of any other type are rejected as business exceptions</t>
+  </si>
+  <si>
+    <t>ACME_CompletedStatus</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Status set on a work item once its hash comment is added</t>
+  </si>
+  <si>
+    <t>ACME_UpdateSuccessText</t>
+  </si>
+  <si>
+    <t>Work Item was updated accordingly</t>
+  </si>
+  <si>
+    <t>Text of the browser alert ACME shows after a successful work item update</t>
+  </si>
+  <si>
+    <t>KillChromeOnRecovery</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>TRUE to force-kill chrome.exe when applications cannot be closed. Keep FALSE on a machine where a person also uses Chrome</t>
+  </si>
+  <si>
+    <t>ExceptionEmail_To</t>
+  </si>
+  <si>
+    <t>Recipient of exception emails (several addresses separated by semicolons). Leave empty to log the message instead of sending it</t>
+  </si>
+  <si>
+    <t>ExceptionEmail_LoginFailedBody</t>
+  </si>
+  <si>
+    <t>Body of the email sent when ACME rejects the login (text from the PDD)</t>
+  </si>
+  <si>
+    <t>SMTP_Server</t>
+  </si>
+  <si>
+    <t>SMTP server used to send exception emails, for example smtp.gmail.com. Leave empty to log the message instead of sending it</t>
+  </si>
+  <si>
+    <t>SMTP_Port</t>
+  </si>
+  <si>
+    <t>587</t>
+  </si>
+  <si>
+    <t>SMTP port (587 for STARTTLS, 465 for SSL)</t>
+  </si>
+  <si>
+    <t>SMTP_CredentialAssetName</t>
+  </si>
+  <si>
+    <t>SMTP_Credential</t>
+  </si>
+  <si>
+    <t>Name of the Orchestrator credential asset holding the sending mailbox address and its password</t>
+  </si>
+  <si>
+    <t>ACME_Portfolio</t>
+  </si>
+  <si>
+    <t>smtp.gmail.com</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Hello, The password or the email is incorrect. Please check and restart Thank you</t>
+  </si>
+  <si>
     <t>ACME_Credential</t>
-  </si>
-  <si>
-    <t>Name of the Orchestrator credential asset for ACME login</t>
-  </si>
-  <si>
-    <t>ACME_URL</t>
-  </si>
-  <si>
-    <t>ACME System 1 URL from Orchestrator text asset</t>
-  </si>
-  <si>
-    <t>SHA1_URL</t>
-  </si>
-  <si>
-    <t>http://www.sha1-online.com/</t>
-  </si>
-  <si>
-    <t>Address of the SHA1 Online hash generator</t>
-  </si>
-  <si>
-    <t>SHA1_Algorithm</t>
-  </si>
-  <si>
-    <t>sha-1</t>
-  </si>
-  <si>
-    <t>Item to select in the hash algorithm dropdown of SHA1 Online</t>
-  </si>
-  <si>
-    <t>ACME_WorkItemType</t>
-  </si>
-  <si>
-    <t>WI5</t>
-  </si>
-  <si>
-    <t>Work item type this process handles; queue items of any other type are rejected as business exceptions</t>
-  </si>
-  <si>
-    <t>ACME_CompletedStatus</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Status set on a work item once its hash comment is added</t>
-  </si>
-  <si>
-    <t>ACME_UpdateSuccessText</t>
-  </si>
-  <si>
-    <t>Work Item was updated accordingly</t>
-  </si>
-  <si>
-    <t>Text of the browser alert ACME shows after a successful work item update</t>
-  </si>
-  <si>
-    <t>KillChromeOnRecovery</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>TRUE to force-kill chrome.exe when applications cannot be closed. Keep FALSE on a machine where a person also uses Chrome</t>
-  </si>
-  <si>
-    <t>ExceptionEmail_To</t>
-  </si>
-  <si>
-    <t>Recipient of exception emails (several addresses separated by semicolons). Leave empty to log the message instead of sending it</t>
-  </si>
-  <si>
-    <t>ExceptionEmail_LoginFailedBody</t>
-  </si>
-  <si>
-    <t>Hello, The username or the email is incorrect. Please check and restart Thank you</t>
-  </si>
-  <si>
-    <t>Body of the email sent when ACME rejects the login (text from the PDD)</t>
-  </si>
-  <si>
-    <t>SMTP_Server</t>
-  </si>
-  <si>
-    <t>SMTP server used to send exception emails, for example smtp.gmail.com. Leave empty to log the message instead of sending it</t>
-  </si>
-  <si>
-    <t>SMTP_Port</t>
-  </si>
-  <si>
-    <t>587</t>
-  </si>
-  <si>
-    <t>SMTP port (587 for STARTTLS, 465 for SSL)</t>
-  </si>
-  <si>
-    <t>SMTP_CredentialAssetName</t>
-  </si>
-  <si>
-    <t>SMTP_Credential</t>
-  </si>
-  <si>
-    <t>Name of the Orchestrator credential asset holding the sending mailbox address and its password</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -295,6 +304,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -313,10 +328,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -326,8 +342,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -698,7 +716,9 @@
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
@@ -720,142 +740,145 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A17" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B17" t="s">
         <v>76</v>
       </c>
+      <c r="C17" s="4" t="s">
+        <v>77</v>
+      </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -1825,7 +1848,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1874,7 +1897,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="28.8">
+    <row r="2" spans="1:26" ht="14.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3036,13 +3059,16 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
